--- a/zeta_personel_listesi.xlsx
+++ b/zeta_personel_listesi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melte\Startkey_Talep_Sistemi\karma_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melte\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9DC725-B1EC-43B4-A476-BA77C99A16DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CCF179-0267-4A6F-B26F-00BDB2825DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="120">
   <si>
     <t>ad_soyad</t>
   </si>
@@ -84,15 +84,6 @@
     <t>meltembulu1981@gmail.com</t>
   </si>
   <si>
-    <t>Ayla Yiğitler</t>
-  </si>
-  <si>
-    <t>ayla.yigitler@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>ayla_yigitler.jpg</t>
-  </si>
-  <si>
     <t>Erhan Yaşar</t>
   </si>
   <si>
@@ -111,15 +102,6 @@
     <t>idil_azbazdar.jpg</t>
   </si>
   <si>
-    <t>İstem Yat</t>
-  </si>
-  <si>
-    <t>istem.yat@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>istem_yat.jpg</t>
-  </si>
-  <si>
     <t>Kemal Yıldız</t>
   </si>
   <si>
@@ -129,39 +111,12 @@
     <t>kemal_yildiz.jpg</t>
   </si>
   <si>
-    <t>Mehtap Öz</t>
-  </si>
-  <si>
-    <t>mehtap.oz@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>mehtap_oz.jpg</t>
-  </si>
-  <si>
-    <t>Merih karayıldırım</t>
-  </si>
-  <si>
-    <t>merih.karayildirim@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>merih_karayildirim.jpg</t>
-  </si>
-  <si>
     <t>Mustafa Balcı</t>
   </si>
   <si>
     <t>mustafa.balci@startkey.com.tr</t>
   </si>
   <si>
-    <t>Erol Özen</t>
-  </si>
-  <si>
-    <t>erol.ozen@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>erol_ozen.jpg</t>
-  </si>
-  <si>
     <t>Işıl Çınar</t>
   </si>
   <si>
@@ -201,15 +156,6 @@
     <t>sinan_yucesoy.jpg</t>
   </si>
   <si>
-    <t>Sümbül Gürel</t>
-  </si>
-  <si>
-    <t>sumbul.gurel@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>sumbul_gurel.jpj</t>
-  </si>
-  <si>
     <t>Turgay Özdemir</t>
   </si>
   <si>
@@ -279,21 +225,12 @@
     <t>a.esatozturk@startkey.com.tr</t>
   </si>
   <si>
-    <t>Ahmet Koca</t>
-  </si>
-  <si>
-    <t>ahmet.koca@startkey.com.tr</t>
-  </si>
-  <si>
     <t>Didem Tekinalp</t>
   </si>
   <si>
     <t>didem.tekinalp@startkey.com.tr</t>
   </si>
   <si>
-    <t>ahmet_koca.jpg</t>
-  </si>
-  <si>
     <t>a.esat_ozturk.jpg</t>
   </si>
   <si>
@@ -321,15 +258,6 @@
     <t>esra_karahasanlar.jpg</t>
   </si>
   <si>
-    <t>Gül Unur</t>
-  </si>
-  <si>
-    <t>gul.unur@startkey.com.tr</t>
-  </si>
-  <si>
-    <t>gul_unur.jpg</t>
-  </si>
-  <si>
     <t>Mustafa Piçakcı</t>
   </si>
   <si>
@@ -378,33 +306,18 @@
     <t>gozde_atilgan</t>
   </si>
   <si>
-    <t>ayla_yigitler</t>
-  </si>
-  <si>
     <t>erhan_yasar</t>
   </si>
   <si>
-    <t>erol_ozen</t>
-  </si>
-  <si>
     <t>isil_cinar</t>
   </si>
   <si>
     <t>idil_azbazdar</t>
   </si>
   <si>
-    <t>istem_yat</t>
-  </si>
-  <si>
     <t>kemal_yildiz</t>
   </si>
   <si>
-    <t>mehtap_oz</t>
-  </si>
-  <si>
-    <t>merih_karayildirim</t>
-  </si>
-  <si>
     <t>mustafa_balci</t>
   </si>
   <si>
@@ -417,18 +330,12 @@
     <t>sinan_yucesoy</t>
   </si>
   <si>
-    <t>sumbul_gurel</t>
-  </si>
-  <si>
     <t>turgay_ozdemir</t>
   </si>
   <si>
     <t>a_esatozturk</t>
   </si>
   <si>
-    <t>ahmet_koca</t>
-  </si>
-  <si>
     <t>didem_tekinalp</t>
   </si>
   <si>
@@ -438,13 +345,46 @@
     <t>esra_karahasanlar</t>
   </si>
   <si>
-    <t>gul_unur</t>
-  </si>
-  <si>
     <t>mustafa_picakci</t>
   </si>
   <si>
     <t>selman_senindikoglu</t>
+  </si>
+  <si>
+    <t>Ahmet Koç</t>
+  </si>
+  <si>
+    <t>ahmet_koc</t>
+  </si>
+  <si>
+    <t>ahmet.koc@startkey.com.tr</t>
+  </si>
+  <si>
+    <t>Arşın Yayman</t>
+  </si>
+  <si>
+    <t>arsin_yayman</t>
+  </si>
+  <si>
+    <t>arsin.yayman@startkey.com.tr</t>
+  </si>
+  <si>
+    <t>Ebru Yayman</t>
+  </si>
+  <si>
+    <t>ebru_yayman</t>
+  </si>
+  <si>
+    <t>ebru.yayman@startkey.com.tr</t>
+  </si>
+  <si>
+    <t>Evrim Kitapçı</t>
+  </si>
+  <si>
+    <t>evrim_kitapci</t>
+  </si>
+  <si>
+    <t>evrim.kitapci@startkey.com.tr</t>
   </si>
 </sst>
 </file>
@@ -796,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.6640625" customWidth="1"/>
@@ -810,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -842,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>18</v>
@@ -851,7 +791,7 @@
         <v>5334125912</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -869,25 +809,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2">
         <v>5334869697</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -897,13 +837,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2">
         <v>5322919415</v>
@@ -915,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
@@ -925,13 +865,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2">
         <v>5050555125</v>
@@ -943,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
@@ -953,13 +893,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2">
         <v>5331958070</v>
@@ -968,10 +908,10 @@
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
@@ -979,15 +919,15 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2">
         <v>5336337318</v>
@@ -999,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
@@ -1009,25 +949,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D8" s="2">
         <v>5523753831</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
@@ -1037,13 +977,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2">
         <v>5304169838</v>
@@ -1055,7 +995,7 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
@@ -1068,13 +1008,13 @@
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="2">
-        <v>5334438496</v>
+        <v>5323819623</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -1095,16 +1035,16 @@
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2">
-        <v>5323819623</v>
+        <v>5335977880</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
@@ -1120,21 +1060,21 @@
         <v>13</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2">
-        <v>5357373531</v>
+        <v>5335220136</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -1150,21 +1090,21 @@
         <v>13</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>96</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="2">
-        <v>5335977880</v>
+        <v>5057734657</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
@@ -1175,26 +1115,25 @@
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>97</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D14" s="2">
-        <v>5335220136</v>
+        <v>5394793514</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -1205,26 +1144,25 @@
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>98</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="D15" s="2">
-        <v>5412816444</v>
+        <v>5332062137</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -1235,26 +1173,25 @@
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2">
-        <v>5057734657</v>
+        <v>5011323186</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -1269,21 +1206,21 @@
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D17" s="2">
-        <v>5405088850</v>
+        <v>5332200401</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
@@ -1298,21 +1235,21 @@
         <v>13</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2">
-        <v>5072112204</v>
+        <v>5337633563</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
@@ -1327,27 +1264,27 @@
         <v>13</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D19" s="2">
-        <v>5394793514</v>
+        <v>5337765450</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1356,27 +1293,27 @@
         <v>13</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2">
-        <v>5332062137</v>
+        <v>5335982149</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1385,27 +1322,27 @@
         <v>13</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2">
-        <v>5011323186</v>
+        <v>5323979703</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1414,27 +1351,27 @@
         <v>13</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2">
-        <v>5332200401</v>
+        <v>5324007435</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1443,27 +1380,27 @@
         <v>13</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2">
-        <v>5374412093</v>
+        <v>5424948765</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1472,79 +1409,76 @@
         <v>13</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2">
-        <v>5337633563</v>
+        <v>5449030884</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5322615009</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="2">
-        <v>5337765450</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D26" s="2">
-        <v>5076328526</v>
+        <v>5397044357</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
@@ -1558,22 +1492,19 @@
       <c r="I26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D27" s="2">
-        <v>5335982149</v>
+        <v>5307695196</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
@@ -1587,22 +1518,19 @@
       <c r="I27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D28" s="2">
-        <v>5323979703</v>
+        <v>5322773549</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
@@ -1615,161 +1543,38 @@
       </c>
       <c r="I28" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="2">
-        <v>5324007435</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="2">
-        <v>5546377094</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="2">
-        <v>5424948765</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="2">
-        <v>5449030884</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{446414FA-C90E-4DE7-BF8C-F846526DEBD4}"/>
-    <hyperlink ref="C10" r:id="rId2" xr:uid="{ACFBD19C-0533-4FA1-B7AB-60107403E5DE}"/>
-    <hyperlink ref="C11" r:id="rId3" xr:uid="{F501CD00-9A5A-48D5-AC3C-D173F32F7DEB}"/>
-    <hyperlink ref="C14" r:id="rId4" xr:uid="{D38C5CF4-71DE-47E1-8776-CA8F25FD86B1}"/>
-    <hyperlink ref="C15" r:id="rId5" xr:uid="{783D50C3-56AB-4CEC-8629-26340634C9A6}"/>
-    <hyperlink ref="C16" r:id="rId6" xr:uid="{72DBB839-22B6-4BA9-BC12-4AB5F10E61CC}"/>
-    <hyperlink ref="C17" r:id="rId7" xr:uid="{7C3A2DB8-220C-4DB8-935B-51D7BCDA494E}"/>
-    <hyperlink ref="C18" r:id="rId8" xr:uid="{1D94DBBB-E6AE-4930-B7A5-A0C4F610F2E8}"/>
-    <hyperlink ref="C19" r:id="rId9" xr:uid="{5E6D60A3-A043-4D19-91FF-BD34A9BD66D2}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{D4D71332-3839-44DA-843F-0D3EDD2D82AB}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{14AC7F32-6EF4-473C-9D92-8157CBF5B497}"/>
-    <hyperlink ref="C20" r:id="rId12" xr:uid="{61C7B1B8-7774-4910-A45C-F6E6835C008C}"/>
-    <hyperlink ref="C21" r:id="rId13" xr:uid="{1B548497-3A9D-46FD-8B1E-D64E076DDA18}"/>
-    <hyperlink ref="C22" r:id="rId14" xr:uid="{2A8471DA-7420-441D-86B2-CC5B4F7C2F93}"/>
-    <hyperlink ref="C23" r:id="rId15" xr:uid="{EDA3A349-BCA1-43AF-B4CC-80DFAA992BAB}"/>
-    <hyperlink ref="C24" r:id="rId16" xr:uid="{A1329F39-7458-4244-B3C5-C2A5D0ECDFC1}"/>
-    <hyperlink ref="C5" r:id="rId17" xr:uid="{1F727AEC-914F-40A4-9CBE-3DE395D35556}"/>
-    <hyperlink ref="C3" r:id="rId18" xr:uid="{81CF557F-C21D-49E9-92AE-FDD33BA0430E}"/>
-    <hyperlink ref="C7" r:id="rId19" xr:uid="{1E4B92CE-2E2B-4B84-B2C4-8D635EBA57AC}"/>
-    <hyperlink ref="C4" r:id="rId20" xr:uid="{77164492-234F-4372-8AD1-D86A90FCF100}"/>
-    <hyperlink ref="C6" r:id="rId21" xr:uid="{4204B664-3051-44DF-A9FC-461486160232}"/>
-    <hyperlink ref="C9" r:id="rId22" xr:uid="{5EFDAAEC-1A17-4FFB-8A3D-BB98F4ADA0EF}"/>
-    <hyperlink ref="C25" r:id="rId23" xr:uid="{0908FEF4-D715-4F71-B03D-AB0CFE729BF1}"/>
-    <hyperlink ref="C26" r:id="rId24" xr:uid="{8816F902-EC53-41DD-8529-62CF4E4164FC}"/>
-    <hyperlink ref="C27" r:id="rId25" xr:uid="{2297BB93-5673-4C81-B321-5B3274E7E9F2}"/>
-    <hyperlink ref="C28" r:id="rId26" xr:uid="{6CB47C07-D70E-4325-9094-7E311A1C4D67}"/>
-    <hyperlink ref="C29" r:id="rId27" xr:uid="{5A620432-95E6-4E3C-AE59-51E866F3A295}"/>
-    <hyperlink ref="C30" r:id="rId28" xr:uid="{D818C47F-3C5F-4AFE-97C9-73619BBF9D44}"/>
-    <hyperlink ref="C31" r:id="rId29" xr:uid="{363753B4-949D-421F-AE85-CDAC50DFFDD2}"/>
-    <hyperlink ref="C32" r:id="rId30" xr:uid="{8E24A087-33E7-4293-9826-34633663B94A}"/>
-    <hyperlink ref="C8" r:id="rId31" xr:uid="{53F20A9C-AFF0-4E89-B2F2-1DA384C7C600}"/>
+    <hyperlink ref="C10" r:id="rId2" xr:uid="{F501CD00-9A5A-48D5-AC3C-D173F32F7DEB}"/>
+    <hyperlink ref="C12" r:id="rId3" xr:uid="{D38C5CF4-71DE-47E1-8776-CA8F25FD86B1}"/>
+    <hyperlink ref="C13" r:id="rId4" xr:uid="{72DBB839-22B6-4BA9-BC12-4AB5F10E61CC}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{5E6D60A3-A043-4D19-91FF-BD34A9BD66D2}"/>
+    <hyperlink ref="C11" r:id="rId6" xr:uid="{14AC7F32-6EF4-473C-9D92-8157CBF5B497}"/>
+    <hyperlink ref="C15" r:id="rId7" xr:uid="{61C7B1B8-7774-4910-A45C-F6E6835C008C}"/>
+    <hyperlink ref="C16" r:id="rId8" xr:uid="{1B548497-3A9D-46FD-8B1E-D64E076DDA18}"/>
+    <hyperlink ref="C17" r:id="rId9" xr:uid="{2A8471DA-7420-441D-86B2-CC5B4F7C2F93}"/>
+    <hyperlink ref="C18" r:id="rId10" xr:uid="{A1329F39-7458-4244-B3C5-C2A5D0ECDFC1}"/>
+    <hyperlink ref="C5" r:id="rId11" xr:uid="{1F727AEC-914F-40A4-9CBE-3DE395D35556}"/>
+    <hyperlink ref="C3" r:id="rId12" xr:uid="{81CF557F-C21D-49E9-92AE-FDD33BA0430E}"/>
+    <hyperlink ref="C7" r:id="rId13" xr:uid="{1E4B92CE-2E2B-4B84-B2C4-8D635EBA57AC}"/>
+    <hyperlink ref="C4" r:id="rId14" xr:uid="{77164492-234F-4372-8AD1-D86A90FCF100}"/>
+    <hyperlink ref="C6" r:id="rId15" xr:uid="{4204B664-3051-44DF-A9FC-461486160232}"/>
+    <hyperlink ref="C9" r:id="rId16" xr:uid="{5EFDAAEC-1A17-4FFB-8A3D-BB98F4ADA0EF}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{0908FEF4-D715-4F71-B03D-AB0CFE729BF1}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{2297BB93-5673-4C81-B321-5B3274E7E9F2}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{6CB47C07-D70E-4325-9094-7E311A1C4D67}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{5A620432-95E6-4E3C-AE59-51E866F3A295}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{363753B4-949D-421F-AE85-CDAC50DFFDD2}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{8E24A087-33E7-4293-9826-34633663B94A}"/>
+    <hyperlink ref="C8" r:id="rId23" xr:uid="{53F20A9C-AFF0-4E89-B2F2-1DA384C7C600}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{C2E19F53-6E18-47EE-A3F2-54AA90E717FB}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{C4800F60-9401-4258-B5B2-AEA8D3171792}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{163786BA-0A50-41C2-9C49-7CE073B8BD29}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{1E020E1F-6A4A-4190-9BD3-F93443CA9411}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
